--- a/TestData/InternationalSchoolFees_TestData.xlsx
+++ b/TestData/InternationalSchoolFees_TestData.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -523,7 +523,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
